--- a/Data/Bronze/MCIC-PROFUNDIZACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 4. EGRESADOS/e. Caracterización e impacto de los egresados/F4_Egresados_Impacto_Profundizacion.xlsx
+++ b/Data/Bronze/MCIC-PROFUNDIZACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 4. EGRESADOS/e. Caracterización e impacto de los egresados/F4_Egresados_Impacto_Profundizacion.xlsx
@@ -9,14 +9,15 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Resumen" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicadores" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Perfil egresados" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sector y vinculación" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instituciones" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Alcance y límites" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Encuesta de impacto" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Perfil egresados" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sector y vinculación" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instituciones" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cobertura" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Privacidad" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Perfil egresados'!$A$4:$O$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Perfil egresados'!$A$4:$O$10</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -25,7 +26,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="8">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -73,14 +74,8 @@
       <color rgb="000B3B60"/>
       <sz val="18"/>
     </font>
-    <font>
-      <name val="Calibri"/>
-      <i val="1"/>
-      <color rgb="004B5563"/>
-      <sz val="9.5"/>
-    </font>
   </fonts>
-  <fills count="6">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -95,11 +90,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00DCE6F1"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFF4E5"/>
       </patternFill>
     </fill>
     <fill>
@@ -178,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -199,13 +189,10 @@
     <xf numFmtId="0" fontId="7" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -573,7 +560,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H16"/>
+  <dimension ref="A1:H13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -593,10 +580,10 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="30" customHeight="1">
+    <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Análisis de la base «Hoja de Vida de Egresados» del módulo institucional de la OATI (146 registros, 145 egresados distintos) separada por modalidad. El archivo fuente (con nombres, documentos y fechas de nacimiento) se resguarda y no se publica.</t>
+          <t>Hoja de Vida de Egresados del módulo institucional de la OATI (6 egresados de Profundización) y encuesta de caracterización e impacto.</t>
         </is>
       </c>
     </row>
@@ -664,88 +651,85 @@
     <row r="9" ht="28" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
-          <t>Egresados OATI (total)</t>
+          <t>Egresados de Profundización (OATI)</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>Egresados de Profundización</t>
+          <t>Con experiencia profesional</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>Plan anterior (sin modalidad)</t>
+          <t>Docentes actuales</t>
         </is>
       </c>
       <c r="G9" s="8" t="inlineStr">
         <is>
-          <t>Sin registro en Cóndor</t>
+          <t>Con ponencias o patentes</t>
         </is>
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
       <c r="A10" s="9" t="n">
-        <v>145</v>
-      </c>
-      <c r="C10" s="9" t="n">
         <v>6</v>
       </c>
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>67 %</t>
+        </is>
+      </c>
       <c r="E10" s="9" t="n">
-        <v>119</v>
+        <v>1</v>
       </c>
       <c r="G10" s="9" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>Con experiencia profesional (Profundización)</t>
+          <t>Cobertura OATI 2022-2026</t>
         </is>
       </c>
       <c r="C12" s="8" t="inlineStr">
         <is>
-          <t>Docentes actuales (Profundización)</t>
+          <t>Respuestas a la encuesta de impacto</t>
         </is>
       </c>
       <c r="E12" s="8" t="inlineStr">
         <is>
-          <t>Con ponencias o patentes (Profundización)</t>
+          <t>Recomendarían la MCIC</t>
         </is>
       </c>
       <c r="G12" s="8" t="inlineStr">
         <is>
-          <t>Cobertura OATI Profundización 2022-2026</t>
+          <t>Aporte alto o muy alto al desarrollo profesional</t>
         </is>
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>67 %</t>
+          <t>2/56</t>
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>1</v>
-      </c>
-      <c r="E13" s="9" t="n">
-        <v>1</v>
+        <v>7</v>
+      </c>
+      <c r="E13" s="9" t="inlineStr">
+        <is>
+          <t>100 %</t>
+        </is>
       </c>
       <c r="G13" s="9" t="inlineStr">
         <is>
-          <t>2/56</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="65" customHeight="1">
-      <c r="A16" s="10" t="inlineStr">
-        <is>
-          <t>La modalidad se obtiene cruzando el documento de cada egresado con Cóndor y las bases MCIC. 119 de 145 egresados terminaron en el plan anterior (énfasis 95-495), antes de que existieran Investigación y Profundización, por lo que no se pueden separar: se muestran como «Plan anterior (sin modalidad)» en ambos libros. La base incluye también personas que hoy están matriculadas, inactivas o suspendidas (docentes y otros), identificadas en la columna «Estado». Con 6 egresados de Profundización los porcentajes son indicativos.</t>
+          <t>100 %</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="26">
+  <mergeCells count="25">
     <mergeCell ref="E12:F12"/>
     <mergeCell ref="G12:H12"/>
     <mergeCell ref="A1:H1"/>
@@ -754,7 +738,6 @@
     <mergeCell ref="A7:B7"/>
     <mergeCell ref="E10:F10"/>
     <mergeCell ref="G10:H10"/>
-    <mergeCell ref="A16:H16"/>
     <mergeCell ref="E13:F13"/>
     <mergeCell ref="C9:D9"/>
     <mergeCell ref="G13:H13"/>
@@ -783,16 +766,14 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G25"/>
+  <dimension ref="A1:E25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="58" customWidth="1" min="1" max="1"/>
     <col width="16" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -805,42 +786,32 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Columna «% Profundización»: porcentaje sobre los egresados de Profundización.</t>
+          <t>Investigación incluye a los egresados del plan anterior. Columna «% Profundización»: porcentaje sobre los egresados de Profundización.</t>
         </is>
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Indicador</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Investigación</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Profundización</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
-        <is>
-          <t>Plan anterior (sin modalidad)</t>
-        </is>
-      </c>
-      <c r="E4" s="11" t="inlineStr">
-        <is>
-          <t>Sin registro en Cóndor</t>
-        </is>
-      </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Total OATI</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>% Profundización</t>
         </is>
@@ -853,48 +824,36 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>18</v>
+        <v>137</v>
       </c>
       <c r="C5" s="6" t="n">
         <v>6</v>
       </c>
       <c r="D5" s="6" t="n">
-        <v>119</v>
-      </c>
-      <c r="E5" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F5" s="6" t="n">
-        <v>145</v>
-      </c>
-      <c r="G5" s="6" t="inlineStr">
+        <v>143</v>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  de ellos, graduados según Cóndor</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
-        <v>14</v>
-      </c>
-      <c r="C6" s="12" t="n">
+      <c r="B6" s="11" t="n">
+        <v>131</v>
+      </c>
+      <c r="C6" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="12" t="n">
-        <v>117</v>
-      </c>
-      <c r="E6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="12" t="n">
+      <c r="D6" s="11" t="n">
         <v>135</v>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>67 %</t>
         </is>
@@ -907,48 +866,36 @@
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="C7" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D7" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="E7" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F7" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" s="6" t="inlineStr">
+        <v>8</v>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
         <is>
           <t>33 %</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>Con experiencia profesional registrada</t>
         </is>
       </c>
-      <c r="B8" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="C8" s="12" t="n">
+      <c r="B8" s="11" t="n">
+        <v>109</v>
+      </c>
+      <c r="C8" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="D8" s="12" t="n">
-        <v>92</v>
-      </c>
-      <c r="E8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="12" t="n">
+      <c r="D8" s="11" t="n">
         <v>113</v>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>67 %</t>
         </is>
@@ -961,48 +908,36 @@
         </is>
       </c>
       <c r="B9" s="6" t="n">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="C9" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D9" s="6" t="n">
-        <v>36</v>
-      </c>
-      <c r="E9" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="6" t="n">
         <v>48</v>
       </c>
-      <c r="G9" s="6" t="inlineStr">
+      <c r="E9" s="6" t="inlineStr">
         <is>
           <t>17 %</t>
         </is>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  vinculación actual en entidad pública</t>
         </is>
       </c>
-      <c r="B10" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="C10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>26</v>
-      </c>
-      <c r="E10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="12" t="n">
+      <c r="B10" s="11" t="n">
         <v>32</v>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="C10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="11" t="n">
+        <v>32</v>
+      </c>
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>0 %</t>
         </is>
@@ -1015,48 +950,36 @@
         </is>
       </c>
       <c r="B11" s="6" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="C11" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D11" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="E11" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="6" t="n">
         <v>16</v>
       </c>
-      <c r="G11" s="6" t="inlineStr">
+      <c r="E11" s="6" t="inlineStr">
         <is>
           <t>17 %</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  vinculación actual en entidad mixta</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="C12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E12" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="12" t="n">
+      <c r="B12" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="G12" s="12" t="inlineStr">
+      <c r="C12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>0 %</t>
         </is>
@@ -1069,48 +992,36 @@
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>15</v>
+        <v>121</v>
       </c>
       <c r="C13" s="6" t="n">
         <v>4</v>
       </c>
       <c r="D13" s="6" t="n">
-        <v>106</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="F13" s="6" t="n">
-        <v>127</v>
-      </c>
-      <c r="G13" s="6" t="inlineStr">
+        <v>125</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>67 %</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  docente actual</t>
         </is>
       </c>
-      <c r="B14" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="C14" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>80</v>
-      </c>
-      <c r="E14" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F14" s="12" t="n">
-        <v>94</v>
-      </c>
-      <c r="G14" s="12" t="inlineStr">
+      <c r="B14" s="11" t="n">
+        <v>91</v>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>92</v>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
         <is>
           <t>17 %</t>
         </is>
@@ -1123,48 +1034,36 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>1</v>
+        <v>36</v>
       </c>
       <c r="C15" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D15" s="6" t="n">
-        <v>35</v>
-      </c>
-      <c r="E15" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F15" s="6" t="n">
-        <v>37</v>
-      </c>
-      <c r="G15" s="6" t="inlineStr">
+        <v>36</v>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>0 %</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="12" t="inlineStr">
+      <c r="A16" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  ha sido docente de la Universidad Distrital</t>
         </is>
       </c>
-      <c r="B16" s="12" t="n">
-        <v>10</v>
-      </c>
-      <c r="C16" s="12" t="n">
+      <c r="B16" s="11" t="n">
+        <v>84</v>
+      </c>
+      <c r="C16" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="12" t="n">
-        <v>74</v>
-      </c>
-      <c r="E16" s="12" t="n">
-        <v>2</v>
-      </c>
-      <c r="F16" s="12" t="n">
-        <v>88</v>
-      </c>
-      <c r="G16" s="12" t="inlineStr">
+      <c r="D16" s="11" t="n">
+        <v>86</v>
+      </c>
+      <c r="E16" s="11" t="inlineStr">
         <is>
           <t>33 %</t>
         </is>
@@ -1177,48 +1076,36 @@
         </is>
       </c>
       <c r="B17" s="6" t="n">
-        <v>13</v>
+        <v>87</v>
       </c>
       <c r="C17" s="6" t="n">
         <v>1</v>
       </c>
       <c r="D17" s="6" t="n">
-        <v>74</v>
-      </c>
-      <c r="E17" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F17" s="6" t="n">
         <v>88</v>
       </c>
-      <c r="G17" s="6" t="inlineStr">
+      <c r="E17" s="6" t="inlineStr">
         <is>
           <t>17 %</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="12" t="inlineStr">
+      <c r="A18" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  con pertenencia a grupo de investigación</t>
         </is>
       </c>
-      <c r="B18" s="12" t="n">
-        <v>11</v>
-      </c>
-      <c r="C18" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D18" s="12" t="n">
-        <v>71</v>
-      </c>
-      <c r="E18" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F18" s="12" t="n">
+      <c r="B18" s="11" t="n">
+        <v>82</v>
+      </c>
+      <c r="C18" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D18" s="11" t="n">
         <v>83</v>
       </c>
-      <c r="G18" s="12" t="inlineStr">
+      <c r="E18" s="11" t="inlineStr">
         <is>
           <t>17 %</t>
         </is>
@@ -1231,48 +1118,36 @@
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>8</v>
+        <v>66</v>
       </c>
       <c r="C19" s="6" t="n">
         <v>0</v>
       </c>
       <c r="D19" s="6" t="n">
-        <v>58</v>
-      </c>
-      <c r="E19" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F19" s="6" t="n">
         <v>66</v>
       </c>
-      <c r="G19" s="6" t="inlineStr">
+      <c r="E19" s="6" t="inlineStr">
         <is>
           <t>0 %</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="12" t="inlineStr">
+      <c r="A20" s="11" t="inlineStr">
         <is>
           <t>Con ponencia internacional</t>
         </is>
       </c>
-      <c r="B20" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="C20" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="12" t="n">
-        <v>20</v>
-      </c>
-      <c r="E20" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="12" t="n">
+      <c r="B20" s="11" t="n">
+        <v>26</v>
+      </c>
+      <c r="C20" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D20" s="11" t="n">
         <v>27</v>
       </c>
-      <c r="G20" s="12" t="inlineStr">
+      <c r="E20" s="11" t="inlineStr">
         <is>
           <t>17 %</t>
         </is>
@@ -1285,48 +1160,36 @@
         </is>
       </c>
       <c r="B21" s="6" t="n">
+        <v>19</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>20</v>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>17 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>Con patente</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="C21" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D21" s="6" t="n">
-        <v>16</v>
-      </c>
-      <c r="E21" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="6" t="n">
-        <v>20</v>
-      </c>
-      <c r="G21" s="6" t="inlineStr">
-        <is>
-          <t>17 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Con patente</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D22" s="12" t="n">
+      <c r="C22" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="E22" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="G22" s="12" t="inlineStr">
+      <c r="E22" s="11" t="inlineStr">
         <is>
           <t>0 %</t>
         </is>
@@ -1339,48 +1202,36 @@
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>12</v>
+        <v>80</v>
       </c>
       <c r="C23" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D23" s="6" t="n">
-        <v>68</v>
-      </c>
-      <c r="E23" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F23" s="6" t="n">
-        <v>83</v>
-      </c>
-      <c r="G23" s="6" t="inlineStr">
+        <v>82</v>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
         <is>
           <t>33 %</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
+      <c r="A24" s="11" t="inlineStr">
         <is>
           <t xml:space="preserve">  con nivel B1 o superior certificado</t>
         </is>
       </c>
-      <c r="B24" s="12" t="n">
-        <v>6</v>
-      </c>
-      <c r="C24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="12" t="n">
-        <v>18</v>
-      </c>
-      <c r="E24" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="F24" s="12" t="n">
+      <c r="B24" s="11" t="n">
         <v>24</v>
       </c>
-      <c r="G24" s="12" t="inlineStr">
+      <c r="C24" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D24" s="11" t="n">
+        <v>24</v>
+      </c>
+      <c r="E24" s="11" t="inlineStr">
         <is>
           <t>0 %</t>
         </is>
@@ -1393,21 +1244,15 @@
         </is>
       </c>
       <c r="B25" s="6" t="n">
-        <v>13</v>
+        <v>94</v>
       </c>
       <c r="C25" s="6" t="n">
         <v>2</v>
       </c>
       <c r="D25" s="6" t="n">
-        <v>81</v>
-      </c>
-      <c r="E25" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F25" s="6" t="n">
         <v>96</v>
       </c>
-      <c r="G25" s="6" t="inlineStr">
+      <c r="E25" s="6" t="inlineStr">
         <is>
           <t>33 %</t>
         </is>
@@ -1415,14 +1260,1619 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H117"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="64" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Encuesta de caracterización e impacto de egresados — Profundización</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>7 respuestas de egresados de Profundización. Sin nombres, documentos ni organizaciones; el texto libre no se publica.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Año de graduación</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
+        <is>
+          <t>Egresados</t>
+        </is>
+      </c>
+      <c r="C5" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="11" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="B7" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" s="11" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>29 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="11" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="B9" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="11" t="inlineStr">
+        <is>
+          <t>43 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>Énfasis</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="30" customHeight="1">
+      <c r="A12" s="10" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>Egresados</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Geomática</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" s="6" t="inlineStr">
+        <is>
+          <t>57 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="11" t="inlineStr">
+        <is>
+          <t>Ingeniería de Software</t>
+        </is>
+      </c>
+      <c r="B14" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C14" s="11" t="inlineStr">
+        <is>
+          <t>29 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Teleinformática</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Grupo de investigación del trabajo de grado</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="30" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="B18" s="10" t="inlineStr">
+        <is>
+          <t>Egresados</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>GIIRA</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>29 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="11" t="inlineStr">
+        <is>
+          <t>NIDE</t>
+        </is>
+      </c>
+      <c r="B20" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C20" s="11" t="inlineStr">
+        <is>
+          <t>29 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>GITEM++</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="11" t="inlineStr">
+        <is>
+          <t>LASER</t>
+        </is>
+      </c>
+      <c r="B22" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" s="11" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>GESETIC</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>Situación principal actual</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="10" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="B26" s="10" t="inlineStr">
+        <is>
+          <t>Egresados</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Docente</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>29 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="11" t="inlineStr">
+        <is>
+          <t>Empleado(a)</t>
+        </is>
+      </c>
+      <c r="B28" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C28" s="11" t="inlineStr">
+        <is>
+          <t>29 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Independiente/consultor(a)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>29 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="11" t="inlineStr">
+        <is>
+          <t>Empleado y Docente</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>Sector en el que se desempeña</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="10" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>Egresados</t>
+        </is>
+      </c>
+      <c r="C33" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Educación Superior</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>29 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
+        <is>
+          <t>Servicios Financieros</t>
+        </is>
+      </c>
+      <c r="B35" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C35" s="11" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>TIC</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
+        <is>
+          <t>Investigación y desarrollo</t>
+        </is>
+      </c>
+      <c r="B37" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="11" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Gobierno/sector público</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
+        <is>
+          <t>Industria</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>Nivel de responsabilidad del cargo</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="10" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="B42" s="10" t="inlineStr">
+        <is>
+          <t>Egresados</t>
+        </is>
+      </c>
+      <c r="C42" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Docencia</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>29 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="11" t="inlineStr">
+        <is>
+          <t>Dirección/jefatura</t>
+        </is>
+      </c>
+      <c r="B44" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C44" s="11" t="inlineStr">
+        <is>
+          <t>29 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Profesional/especialista</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C45" s="6" t="inlineStr">
+        <is>
+          <t>29 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="11" t="inlineStr">
+        <is>
+          <t>Emprendimiento</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>Relación de la actividad actual con la formación recibida</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="30" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="B49" s="10" t="inlineStr">
+        <is>
+          <t>Egresados</t>
+        </is>
+      </c>
+      <c r="C49" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Muy Relacionada</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>57 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="11" t="inlineStr">
+        <is>
+          <t>Totalmente Relacionada</t>
+        </is>
+      </c>
+      <c r="B51" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C51" s="11" t="inlineStr">
+        <is>
+          <t>29 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="6" t="inlineStr">
+        <is>
+          <t>No relacionada</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C52" s="6" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="3" t="inlineStr">
+        <is>
+          <t>Aporte de la MCIC a su desarrollo (número de egresados por nivel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="30" customHeight="1">
+      <c r="A55" s="10" t="inlineStr">
+        <is>
+          <t>Dimensión</t>
+        </is>
+      </c>
+      <c r="B55" s="10" t="inlineStr">
+        <is>
+          <t>Muy alto</t>
+        </is>
+      </c>
+      <c r="C55" s="10" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="D55" s="10" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="E55" s="10" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="F55" s="10" t="inlineStr">
+        <is>
+          <t>Ningún aporte</t>
+        </is>
+      </c>
+      <c r="G55" s="10" t="inlineStr">
+        <is>
+          <t>% Alto o Muy alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Desarrollo profesional</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C56" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="6" t="inlineStr">
+        <is>
+          <t>100 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>Acceso a nuevas oportunidades laborales</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C57" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D57" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E57" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F57" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="11" t="inlineStr">
+        <is>
+          <t>71 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Capacidad para resolver problemas complejos</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E58" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F58" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G58" s="6" t="inlineStr">
+        <is>
+          <t>71 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>Desarrollo de capacidades de investigación</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C59" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G59" s="11" t="inlineStr">
+        <is>
+          <t>86 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Innovación y desarrollo tecnológico</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C60" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="6" t="inlineStr">
+        <is>
+          <t>86 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>Liderazgo de proyectos</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C61" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D61" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F61" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="11" t="inlineStr">
+        <is>
+          <t>57 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Toma de decisiones basada en información</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C62" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="D62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="6" t="inlineStr">
+        <is>
+          <t>86 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo interdisciplinario</t>
+        </is>
+      </c>
+      <c r="B63" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C63" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D63" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F63" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="11" t="inlineStr">
+        <is>
+          <t>71 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Desarrollo de redes académicas/profesionales</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C64" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E64" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G64" s="6" t="inlineStr">
+        <is>
+          <t>43 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
+          <t>Continuación de estudios de formación avanzada</t>
+        </is>
+      </c>
+      <c r="B65" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="D65" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E65" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G65" s="11" t="inlineStr">
+        <is>
+          <t>43 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Generación o transferencia de conocimiento</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C66" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D66" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G66" s="6" t="inlineStr">
+        <is>
+          <t>71 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Actividades después de graduarse (selección múltiple)</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="30" customHeight="1">
+      <c r="A69" s="10" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="B69" s="10" t="inlineStr">
+        <is>
+          <t>Egresados</t>
+        </is>
+      </c>
+      <c r="C69" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Desarrollo de software o soluciones tecnológicas</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C70" s="6" t="inlineStr">
+        <is>
+          <t>71 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="11" t="inlineStr">
+        <is>
+          <t>Docencia universitaria</t>
+        </is>
+      </c>
+      <c r="B71" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C71" s="11" t="inlineStr">
+        <is>
+          <t>43 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Innovaciones o mejoras de procesos</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C72" s="6" t="inlineStr">
+        <is>
+          <t>29 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="11" t="inlineStr">
+        <is>
+          <t>Participación en proyectos con entidades públicas o privadas</t>
+        </is>
+      </c>
+      <c r="B73" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C73" s="11" t="inlineStr">
+        <is>
+          <t>29 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="6" t="inlineStr">
+        <is>
+          <t>Dirección o participación en proyectos de impacto social</t>
+        </is>
+      </c>
+      <c r="B74" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C74" s="6" t="inlineStr">
+        <is>
+          <t>29 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="11" t="inlineStr">
+        <is>
+          <t>Participación en redes académicas o profesionales</t>
+        </is>
+      </c>
+      <c r="B75" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C75" s="11" t="inlineStr">
+        <is>
+          <t>29 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Patentes, registros de software u otros productos de propiedad intelectual</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C76" s="6" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="11" t="inlineStr">
+        <is>
+          <t>Consultorías especializadas</t>
+        </is>
+      </c>
+      <c r="B77" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C77" s="11" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Dirección de trabajos de grado</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C78" s="6" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="11" t="inlineStr">
+        <is>
+          <t>Ponencias en eventos internacionales.</t>
+        </is>
+      </c>
+      <c r="B79" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="11" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Creación de empresa/emprendimiento</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" s="6" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="11" t="inlineStr">
+        <is>
+          <t>Ponencias en eventos nacionales.</t>
+        </is>
+      </c>
+      <c r="B81" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" s="11" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Jurado de Tesis</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" s="6" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>Formación continuada después de graduarse (selección múltiple)</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="30" customHeight="1">
+      <c r="A85" s="10" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="B85" s="10" t="inlineStr">
+        <is>
+          <t>Egresados</t>
+        </is>
+      </c>
+      <c r="C85" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B86" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C86" s="6" t="inlineStr">
+        <is>
+          <t>100 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="11" t="inlineStr">
+        <is>
+          <t>Curso / diplomados</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" s="11" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="3" t="inlineStr">
+        <is>
+          <t>Pertenece o ha pertenecido a un grupo de investigación</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="30" customHeight="1">
+      <c r="A90" s="10" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="B90" s="10" t="inlineStr">
+        <is>
+          <t>Egresados</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B91" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C91" s="6" t="inlineStr">
+        <is>
+          <t>86 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="B92" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C92" s="11" t="inlineStr">
+        <is>
+          <t>14 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="3" t="inlineStr">
+        <is>
+          <t>Ha publicado productos académicos o científicos después de graduarse</t>
+        </is>
+      </c>
+    </row>
+    <row r="95" ht="30" customHeight="1">
+      <c r="A95" s="10" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="B95" s="10" t="inlineStr">
+        <is>
+          <t>Egresados</t>
+        </is>
+      </c>
+      <c r="C95" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B96" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="C96" s="6" t="inlineStr">
+        <is>
+          <t>100 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="3" t="inlineStr">
+        <is>
+          <t>Valoración de la formación (escala 1 a 5)</t>
+        </is>
+      </c>
+    </row>
+    <row r="99" ht="30" customHeight="1">
+      <c r="A99" s="10" t="inlineStr">
+        <is>
+          <t>Aspecto</t>
+        </is>
+      </c>
+      <c r="B99" s="10" t="inlineStr">
+        <is>
+          <t>Promedio</t>
+        </is>
+      </c>
+      <c r="C99" s="10" t="inlineStr">
+        <is>
+          <t>Respuestas</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="6" t="inlineStr">
+        <is>
+          <t>Pertinencia de la formación recibida</t>
+        </is>
+      </c>
+      <c r="B100" s="6" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="C100" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="11" t="inlineStr">
+        <is>
+          <t>Actualidad de los conocimientos adquiridos</t>
+        </is>
+      </c>
+      <c r="B101" s="11" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="C101" s="11" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="6" t="inlineStr">
+        <is>
+          <t>Contribución de la Maestría a su desempeño profesional</t>
+        </is>
+      </c>
+      <c r="B102" s="6" t="n">
+        <v>4.71</v>
+      </c>
+      <c r="C102" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="11" t="inlineStr">
+        <is>
+          <t>Contribución a sus capacidades investigativas</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="n">
+        <v>4.43</v>
+      </c>
+      <c r="C103" s="11" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="6" t="inlineStr">
+        <is>
+          <t>Contribución a su capacidad de innovación</t>
+        </is>
+      </c>
+      <c r="B104" s="6" t="n">
+        <v>4.29</v>
+      </c>
+      <c r="C104" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="11" t="inlineStr">
+        <is>
+          <t>Reconocimiento de la MCIC en su entorno profesional</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C105" s="11" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="6" t="inlineStr">
+        <is>
+          <t>Correspondencia entre la formación recibida y las necesidades actuales del entorno</t>
+        </is>
+      </c>
+      <c r="B106" s="6" t="n">
+        <v>4.57</v>
+      </c>
+      <c r="C106" s="6" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="3" t="inlineStr">
+        <is>
+          <t>¿Recomendaría la MCIC a otros profesionales?</t>
+        </is>
+      </c>
+    </row>
+    <row r="109" ht="30" customHeight="1">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="B109" s="10" t="inlineStr">
+        <is>
+          <t>Egresados</t>
+        </is>
+      </c>
+      <c r="C109" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="6" t="inlineStr">
+        <is>
+          <t>Definitivamente sí</t>
+        </is>
+      </c>
+      <c r="B110" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C110" s="6" t="inlineStr">
+        <is>
+          <t>71 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="11" t="inlineStr">
+        <is>
+          <t>Probablemente sí</t>
+        </is>
+      </c>
+      <c r="B111" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C111" s="11" t="inlineStr">
+        <is>
+          <t>29 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="3" t="inlineStr">
+        <is>
+          <t>¿Ha generado algún impacto en su entorno a partir de su formación?</t>
+        </is>
+      </c>
+    </row>
+    <row r="114" ht="30" customHeight="1">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="B114" s="10" t="inlineStr">
+        <is>
+          <t>Egresados</t>
+        </is>
+      </c>
+      <c r="C114" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="B115" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C115" s="6" t="inlineStr">
+        <is>
+          <t>43 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="11" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>29 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="6" t="inlineStr">
+        <is>
+          <t>Parcialmente</t>
+        </is>
+      </c>
+      <c r="B117" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C117" s="6" t="inlineStr">
+        <is>
+          <t>29 %</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="17">
+    <mergeCell ref="A94:H94"/>
+    <mergeCell ref="A4:H4"/>
+    <mergeCell ref="A48:H48"/>
+    <mergeCell ref="A84:H84"/>
+    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A113:H113"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A54:H54"/>
+    <mergeCell ref="A98:H98"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="A68:H68"/>
+    <mergeCell ref="A11:H11"/>
+    <mergeCell ref="A108:H108"/>
+    <mergeCell ref="A1:H1"/>
+    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A89:H89"/>
+    <mergeCell ref="A17:H17"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1463,77 +2913,77 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>ID</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Énfasis (plan de ingreso)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Estado en Cóndor</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Año de grado (est.)</t>
         </is>
       </c>
-      <c r="E4" s="11" t="inlineStr">
+      <c r="E4" s="10" t="inlineStr">
         <is>
           <t>Vinculación actual</t>
         </is>
       </c>
-      <c r="F4" s="11" t="inlineStr">
+      <c r="F4" s="10" t="inlineStr">
         <is>
           <t>Tipo de entidad</t>
         </is>
       </c>
-      <c r="G4" s="11" t="inlineStr">
+      <c r="G4" s="10" t="inlineStr">
         <is>
           <t>Sector estimado</t>
         </is>
       </c>
-      <c r="H4" s="11" t="inlineStr">
+      <c r="H4" s="10" t="inlineStr">
         <is>
           <t>Docente actual</t>
         </is>
       </c>
-      <c r="I4" s="11" t="inlineStr">
+      <c r="I4" s="10" t="inlineStr">
         <is>
           <t>Niveles de docencia</t>
         </is>
       </c>
-      <c r="J4" s="11" t="inlineStr">
+      <c r="J4" s="10" t="inlineStr">
         <is>
           <t>Grupos de investigación</t>
         </is>
       </c>
-      <c r="K4" s="11" t="inlineStr">
+      <c r="K4" s="10" t="inlineStr">
         <is>
           <t>Proyectos de investigación</t>
         </is>
       </c>
-      <c r="L4" s="11" t="inlineStr">
+      <c r="L4" s="10" t="inlineStr">
         <is>
           <t>Ponencias</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr">
+      <c r="M4" s="10" t="inlineStr">
         <is>
           <t>Patentes</t>
         </is>
       </c>
-      <c r="N4" s="11" t="inlineStr">
+      <c r="N4" s="10" t="inlineStr">
         <is>
           <t>Mejor nivel de inglés/2ª lengua</t>
         </is>
       </c>
-      <c r="O4" s="11" t="inlineStr">
+      <c r="O4" s="10" t="inlineStr">
         <is>
           <t>Secciones diligenciadas</t>
         </is>
@@ -1609,69 +3059,69 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>E-002</t>
         </is>
       </c>
-      <c r="B6" s="12" t="inlineStr">
+      <c r="B6" s="11" t="inlineStr">
         <is>
           <t>Teleinformática</t>
         </is>
       </c>
-      <c r="C6" s="12" t="inlineStr">
+      <c r="C6" s="11" t="inlineStr">
         <is>
           <t>Matriculado</t>
         </is>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E6" s="12" t="inlineStr">
+      <c r="E6" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F6" s="12" t="inlineStr">
+      <c r="F6" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G6" s="12" t="inlineStr">
+      <c r="G6" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H6" s="12" t="inlineStr">
+      <c r="H6" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I6" s="12" t="inlineStr">
+      <c r="I6" s="11" t="inlineStr">
         <is>
           <t>Pregrado</t>
         </is>
       </c>
-      <c r="J6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N6" s="12" t="inlineStr">
+      <c r="J6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O6" s="12" t="inlineStr">
+      <c r="O6" s="11" t="inlineStr">
         <is>
           <t>2/4</t>
         </is>
@@ -1745,65 +3195,65 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
+      <c r="A8" s="11" t="inlineStr">
         <is>
           <t>E-004</t>
         </is>
       </c>
-      <c r="B8" s="12" t="inlineStr">
+      <c r="B8" s="11" t="inlineStr">
         <is>
           <t>Geomática</t>
         </is>
       </c>
-      <c r="C8" s="12" t="inlineStr">
+      <c r="C8" s="11" t="inlineStr">
         <is>
           <t>Graduado</t>
         </is>
       </c>
-      <c r="D8" s="12" t="n">
+      <c r="D8" s="11" t="n">
         <v>2021</v>
       </c>
-      <c r="E8" s="12" t="inlineStr">
+      <c r="E8" s="11" t="inlineStr">
         <is>
           <t>Sí</t>
         </is>
       </c>
-      <c r="F8" s="12" t="inlineStr">
+      <c r="F8" s="11" t="inlineStr">
         <is>
           <t>Privada</t>
         </is>
       </c>
-      <c r="G8" s="12" t="inlineStr">
+      <c r="G8" s="11" t="inlineStr">
         <is>
           <t>Sin clasificar</t>
         </is>
       </c>
-      <c r="H8" s="12" t="inlineStr">
+      <c r="H8" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I8" s="12" t="inlineStr">
+      <c r="I8" s="11" t="inlineStr">
         <is>
           <t>Pregrado</t>
         </is>
       </c>
-      <c r="J8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="12" t="n">
+      <c r="J8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="11" t="n">
         <v/>
       </c>
-      <c r="O8" s="12" t="inlineStr">
+      <c r="O8" s="11" t="inlineStr">
         <is>
           <t>3/4</t>
         </is>
@@ -1877,67 +3327,67 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="12" t="inlineStr">
+      <c r="A10" s="11" t="inlineStr">
         <is>
           <t>E-006</t>
         </is>
       </c>
-      <c r="B10" s="12" t="inlineStr">
+      <c r="B10" s="11" t="inlineStr">
         <is>
           <t>Ingeniería de Software</t>
         </is>
       </c>
-      <c r="C10" s="12" t="inlineStr">
+      <c r="C10" s="11" t="inlineStr">
         <is>
           <t>Graduado</t>
         </is>
       </c>
-      <c r="D10" s="12" t="n">
+      <c r="D10" s="11" t="n">
         <v>2026</v>
       </c>
-      <c r="E10" s="12" t="inlineStr">
+      <c r="E10" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="F10" s="12" t="inlineStr">
+      <c r="F10" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G10" s="12" t="inlineStr">
+      <c r="G10" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H10" s="12" t="inlineStr">
+      <c r="H10" s="11" t="inlineStr">
         <is>
           <t>No</t>
         </is>
       </c>
-      <c r="I10" s="12" t="inlineStr">
+      <c r="I10" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="J10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="12" t="inlineStr">
+      <c r="J10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="11" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="O10" s="12" t="inlineStr">
+      <c r="O10" s="11" t="inlineStr">
         <is>
           <t>0/4</t>
         </is>
@@ -1948,232 +3398,6 @@
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
     <mergeCell ref="A2:O2"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F24"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="14" customWidth="1" min="2" max="2"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="24" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Dónde trabajan los egresados (sector estimado por nombre de la entidad)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="30" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>El módulo no tiene un campo de sector económico: se estimó por palabras clave en el nombre de la entidad. Quedan «Sin clasificar» los nombres que no permiten inferirlo.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>Vinculación actual — Profundización</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="11" t="inlineStr">
-        <is>
-          <t>Sector estimado</t>
-        </is>
-      </c>
-      <c r="B5" s="11" t="inlineStr">
-        <is>
-          <t>Egresados</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Sin clasificar</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>Trayectoria profesional (todas las experiencias) — Profundización</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="11" t="inlineStr">
-        <is>
-          <t>Sector estimado</t>
-        </is>
-      </c>
-      <c r="B9" s="11" t="inlineStr">
-        <is>
-          <t>Egresados con experiencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="6" t="inlineStr">
-        <is>
-          <t>Gobierno y entidades públicas</t>
-        </is>
-      </c>
-      <c r="B10" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="12" t="inlineStr">
-        <is>
-          <t>Sin clasificar</t>
-        </is>
-      </c>
-      <c r="B11" s="12" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="6" t="inlineStr">
-        <is>
-          <t>Geoinformación, consultoría e ingeniería</t>
-        </is>
-      </c>
-      <c r="B12" s="6" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="12" t="inlineStr">
-        <is>
-          <t>Telecomunicaciones y TIC</t>
-        </is>
-      </c>
-      <c r="B13" s="12" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>Plan anterior (compartido) — trayectoria profesional</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="11" t="inlineStr">
-        <is>
-          <t>Sector estimado</t>
-        </is>
-      </c>
-      <c r="B16" s="11" t="inlineStr">
-        <is>
-          <t>Egresados con experiencia</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
-        <is>
-          <t>Sin clasificar</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="12" t="inlineStr">
-        <is>
-          <t>Educación</t>
-        </is>
-      </c>
-      <c r="B18" s="12" t="n">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="6" t="inlineStr">
-        <is>
-          <t>Gobierno y entidades públicas</t>
-        </is>
-      </c>
-      <c r="B19" s="6" t="n">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="12" t="inlineStr">
-        <is>
-          <t>Telecomunicaciones y TIC</t>
-        </is>
-      </c>
-      <c r="B20" s="12" t="n">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="6" t="inlineStr">
-        <is>
-          <t>Geoinformación, consultoría e ingeniería</t>
-        </is>
-      </c>
-      <c r="B21" s="6" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Financiero y seguros</t>
-        </is>
-      </c>
-      <c r="B22" s="12" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="6" t="inlineStr">
-        <is>
-          <t>Energía y servicios públicos</t>
-        </is>
-      </c>
-      <c r="B23" s="6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>Salud</t>
-        </is>
-      </c>
-      <c r="B24" s="12" t="n">
-        <v>2</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="5">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A8:D8"/>
-    <mergeCell ref="A4:D4"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A15:D15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2185,415 +3409,121 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D42"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="60" customWidth="1" min="1" max="1"/>
-    <col width="12" customWidth="1" min="2" max="2"/>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Instituciones donde han trabajado o dictado docencia los egresados (todas las modalidades)</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="16" customHeight="1">
+          <t>Dónde trabajan los egresados (sector estimado por nombre de la entidad)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="30" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Conteo de egresados distintos por institución (las 25 principales con 2 o más egresados); no se asocia a personas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
-        <is>
-          <t>Experiencia profesional — institución</t>
-        </is>
-      </c>
-      <c r="B4" s="11" t="inlineStr">
+          <t>El módulo no tiene un campo de sector económico: se estimó por palabras clave en el nombre de la entidad. Quedan «Sin clasificar» los nombres que no permiten inferirlo.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>Vinculación actual — Profundización</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
+      <c r="A5" s="10" t="inlineStr">
+        <is>
+          <t>Sector estimado</t>
+        </is>
+      </c>
+      <c r="B5" s="10" t="inlineStr">
         <is>
           <t>Egresados</t>
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="6" t="inlineStr">
-        <is>
-          <t>Universidad Distrital Francisco José de Caldas</t>
-        </is>
-      </c>
-      <c r="B5" s="6" t="n">
-        <v>47</v>
-      </c>
-    </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
-        <is>
-          <t>Instituto Geográfico Agustín Codazzi (IGAC)</t>
-        </is>
-      </c>
-      <c r="B6" s="12" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="6" t="inlineStr">
-        <is>
-          <t>Universidad ECCI</t>
-        </is>
-      </c>
-      <c r="B7" s="6" t="n">
-        <v>4</v>
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Sena</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="n">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>Trayectoria profesional (todas las experiencias) — Profundización</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="30" customHeight="1">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Sector estimado</t>
+        </is>
+      </c>
+      <c r="B9" s="10" t="inlineStr">
+        <is>
+          <t>Egresados con experiencia</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Gobierno y entidades públicas</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="6" t="inlineStr">
-        <is>
-          <t>UNIMINUTO</t>
-        </is>
-      </c>
-      <c r="B9" s="6" t="n">
+    <row r="11">
+      <c r="A11" s="11" t="inlineStr">
+        <is>
+          <t>Sin clasificar</t>
+        </is>
+      </c>
+      <c r="B11" s="11" t="n">
         <v>2</v>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="12" t="inlineStr">
-        <is>
-          <t>Comware</t>
-        </is>
-      </c>
-      <c r="B10" s="12" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="6" t="inlineStr">
-        <is>
-          <t>Telefónica</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
     <row r="12">
-      <c r="A12" s="12" t="inlineStr">
-        <is>
-          <t>Ministerio de Comunicaciones</t>
-        </is>
-      </c>
-      <c r="B12" s="12" t="n">
-        <v>2</v>
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Geoinformación, consultoría e ingeniería</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
-        <is>
-          <t>Instituto Nacional de Salud</t>
-        </is>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>UPTC</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
-        <is>
-          <t>Departamento Nacional de Planeación</t>
-        </is>
-      </c>
-      <c r="B15" s="6" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
-        <is>
-          <t>Docencia — institución</t>
-        </is>
-      </c>
-      <c r="B17" s="11" t="inlineStr">
-        <is>
-          <t>Egresados</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Universidad Distrital Francisco José de Caldas</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="n">
-        <v>88</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Universidad ECCI</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="n">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>SENA</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Fundacion Universitaria los Libertadores</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="n">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="6" t="inlineStr">
-        <is>
-          <t>Universidad Antonio Nariño</t>
-        </is>
-      </c>
-      <c r="B22" s="6" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>FUAC</t>
-        </is>
-      </c>
-      <c r="B23" s="12" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="6" t="inlineStr">
-        <is>
-          <t>Universidad Cooperativa de Colombia</t>
-        </is>
-      </c>
-      <c r="B24" s="6" t="n">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="12" t="inlineStr">
-        <is>
-          <t>Universidad Santo Tomas</t>
-        </is>
-      </c>
-      <c r="B25" s="12" t="n">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="6" t="inlineStr">
-        <is>
-          <t>Corporacion Universitaria Unitec</t>
-        </is>
-      </c>
-      <c r="B26" s="6" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="12" t="inlineStr">
-        <is>
-          <t>UNIMINUTO</t>
-        </is>
-      </c>
-      <c r="B27" s="12" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="6" t="inlineStr">
-        <is>
-          <t>UNAD</t>
-        </is>
-      </c>
-      <c r="B28" s="6" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="12" t="inlineStr">
-        <is>
-          <t>Universidad Catolica de Colombia</t>
-        </is>
-      </c>
-      <c r="B29" s="12" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="6" t="inlineStr">
-        <is>
-          <t>Universidad Militar-nueva Granada</t>
-        </is>
-      </c>
-      <c r="B30" s="6" t="n">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>Universidad el Bosque</t>
-        </is>
-      </c>
-      <c r="B31" s="12" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="6" t="inlineStr">
-        <is>
-          <t>Fundacion Universitaria Konrad Lorenz</t>
-        </is>
-      </c>
-      <c r="B32" s="6" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="12" t="inlineStr">
-        <is>
-          <t>Fundación Universitaria Compensar</t>
-        </is>
-      </c>
-      <c r="B33" s="12" t="n">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Universidad Sergio Arboleda</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>Universidad Manuela Beltran-umb</t>
-        </is>
-      </c>
-      <c r="B35" s="12" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="6" t="inlineStr">
-        <is>
-          <t>Universidad de la Salle</t>
-        </is>
-      </c>
-      <c r="B36" s="6" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="12" t="inlineStr">
-        <is>
-          <t>UPTC</t>
-        </is>
-      </c>
-      <c r="B37" s="12" t="n">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="6" t="inlineStr">
-        <is>
-          <t>UDCA</t>
-        </is>
-      </c>
-      <c r="B38" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="12" t="inlineStr">
-        <is>
-          <t>Universidad de Cundinamarca-udec</t>
-        </is>
-      </c>
-      <c r="B39" s="12" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="6" t="inlineStr">
-        <is>
-          <t>Politecnico Grancolombiano</t>
-        </is>
-      </c>
-      <c r="B40" s="6" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="12" t="inlineStr">
-        <is>
-          <t>Universidad Nacional de Colombia</t>
-        </is>
-      </c>
-      <c r="B41" s="12" t="n">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="6" t="inlineStr">
-        <is>
-          <t>Fundacion Universitaria SAN Martin</t>
-        </is>
-      </c>
-      <c r="B42" s="6" t="n">
-        <v>3</v>
+      <c r="A13" s="11" t="inlineStr">
+        <is>
+          <t>Telecomunicaciones y TIC</t>
+        </is>
+      </c>
+      <c r="B13" s="11" t="n">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A2:D2"/>
+  <mergeCells count="4">
+    <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A4:D4"/>
+    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A8:D8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2605,7 +3535,87 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:D8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="60" customWidth="1" min="1" max="1"/>
+    <col width="12" customWidth="1" min="2" max="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Instituciones donde han trabajado o dictado docencia los egresados de Profundización</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="16" customHeight="1">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Conteo de egresados distintos por institución (las 25 principales con 2 o más egresados); no se asocia a personas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="10" t="inlineStr">
+        <is>
+          <t>Experiencia profesional — institución</t>
+        </is>
+      </c>
+      <c r="B4" s="10" t="inlineStr">
+        <is>
+          <t>Egresados</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Instituto Geográfico Agustín Codazzi (IGAC)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" ht="30" customHeight="1">
+      <c r="A7" s="10" t="inlineStr">
+        <is>
+          <t>Docencia — institución</t>
+        </is>
+      </c>
+      <c r="B7" s="10" t="inlineStr">
+        <is>
+          <t>Egresados</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Universidad Distrital Francisco José de Caldas</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>2</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A2:D2"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -2630,22 +3640,22 @@
       </c>
     </row>
     <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="11" t="inlineStr">
+      <c r="A4" s="10" t="inlineStr">
         <is>
           <t>Grupo</t>
         </is>
       </c>
-      <c r="B4" s="11" t="inlineStr">
+      <c r="B4" s="10" t="inlineStr">
         <is>
           <t>Graduados (Cóndor)</t>
         </is>
       </c>
-      <c r="C4" s="11" t="inlineStr">
+      <c r="C4" s="10" t="inlineStr">
         <is>
           <t>Con Hoja de Vida (OATI)</t>
         </is>
       </c>
-      <c r="D4" s="11" t="inlineStr">
+      <c r="D4" s="10" t="inlineStr">
         <is>
           <t>Cobertura</t>
         </is>
@@ -2658,30 +3668,30 @@
         </is>
       </c>
       <c r="B5" s="6" t="n">
-        <v>76</v>
+        <v>502</v>
       </c>
       <c r="C5" s="6" t="n">
-        <v>14</v>
+        <v>131</v>
       </c>
       <c r="D5" s="6" t="inlineStr">
         <is>
-          <t>18 %</t>
+          <t>26 %</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="12" t="inlineStr">
+      <c r="A6" s="11" t="inlineStr">
         <is>
           <t>Profundización</t>
         </is>
       </c>
-      <c r="B6" s="12" t="n">
+      <c r="B6" s="11" t="n">
         <v>75</v>
       </c>
-      <c r="C6" s="12" t="n">
+      <c r="C6" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="D6" s="12" t="inlineStr">
+      <c r="D6" s="11" t="inlineStr">
         <is>
           <t>5 %</t>
         </is>
@@ -2690,300 +3700,167 @@
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>Plan anterior (sin modalidad)</t>
+          <t>Total</t>
         </is>
       </c>
       <c r="B7" s="6" t="n">
-        <v>426</v>
+        <v>577</v>
       </c>
       <c r="C7" s="6" t="n">
-        <v>117</v>
+        <v>135</v>
       </c>
       <c r="D7" s="6" t="inlineStr">
         <is>
-          <t>27 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="12" t="inlineStr">
-        <is>
-          <t>Total</t>
-        </is>
-      </c>
-      <c r="B8" s="12" t="n">
-        <v>577</v>
-      </c>
-      <c r="C8" s="12" t="n">
-        <v>135</v>
-      </c>
-      <c r="D8" s="12" t="inlineStr">
-        <is>
           <t>23 %</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>Graduados por año de grado estimado (última matrícula) — Profundización y plan anterior</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="11" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>Graduados por año de grado estimado (última matrícula) — Profundización</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="30" customHeight="1">
+      <c r="A10" s="10" t="inlineStr">
         <is>
           <t>Grupo</t>
         </is>
       </c>
-      <c r="B11" s="11" t="inlineStr">
+      <c r="B10" s="10" t="inlineStr">
         <is>
           <t>Año</t>
         </is>
       </c>
-      <c r="C11" s="11" t="inlineStr">
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>Graduados (Cóndor)</t>
         </is>
       </c>
-      <c r="D11" s="11" t="inlineStr">
+      <c r="D10" s="10" t="inlineStr">
         <is>
           <t>Con Hoja de Vida (OATI)</t>
         </is>
       </c>
-      <c r="E11" s="11" t="inlineStr">
+      <c r="E10" s="10" t="inlineStr">
         <is>
           <t>Cobertura</t>
         </is>
       </c>
     </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Profundización</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="inlineStr">
+        <is>
+          <t>2022</t>
+        </is>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="6" t="inlineStr">
+        <is>
+          <t>0 %</t>
+        </is>
+      </c>
+    </row>
     <row r="12">
-      <c r="A12" s="6" t="inlineStr">
+      <c r="A12" s="11" t="inlineStr">
         <is>
           <t>Profundización</t>
         </is>
       </c>
-      <c r="B12" s="6" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="C12" s="6" t="n">
-        <v>9</v>
-      </c>
-      <c r="D12" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="6" t="inlineStr">
+      <c r="B12" s="11" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="C12" s="11" t="n">
+        <v>15</v>
+      </c>
+      <c r="D12" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="11" t="inlineStr">
         <is>
           <t>0 %</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="12" t="inlineStr">
+      <c r="A13" s="6" t="inlineStr">
         <is>
           <t>Profundización</t>
         </is>
       </c>
-      <c r="B13" s="12" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="C13" s="12" t="n">
-        <v>15</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="12" t="inlineStr">
+      <c r="B13" s="6" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="6" t="inlineStr">
         <is>
           <t>0 %</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>Profundización</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="C14" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="D14" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="6" t="inlineStr">
-        <is>
-          <t>0 %</t>
+      <c r="B14" s="11" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="C14" s="11" t="n">
+        <v>17</v>
+      </c>
+      <c r="D14" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="E14" s="11" t="inlineStr">
+        <is>
+          <t>6 %</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="12" t="inlineStr">
+      <c r="A15" s="6" t="inlineStr">
         <is>
           <t>Profundización</t>
         </is>
       </c>
-      <c r="B15" s="12" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C15" s="12" t="n">
-        <v>17</v>
-      </c>
-      <c r="D15" s="12" t="n">
-        <v>1</v>
-      </c>
-      <c r="E15" s="12" t="inlineStr">
-        <is>
-          <t>6 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
-        <is>
-          <t>Profundización</t>
-        </is>
-      </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B15" s="6" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="C16" s="6" t="n">
+      <c r="C15" s="6" t="n">
         <v>10</v>
       </c>
-      <c r="D16" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="D15" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
         <is>
           <t>10 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="12" t="inlineStr">
-        <is>
-          <t>Plan anterior (sin modalidad)</t>
-        </is>
-      </c>
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>2022</t>
-        </is>
-      </c>
-      <c r="C17" s="12" t="n">
-        <v>13</v>
-      </c>
-      <c r="D17" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="E17" s="12" t="inlineStr">
-        <is>
-          <t>23 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
-        <is>
-          <t>Plan anterior (sin modalidad)</t>
-        </is>
-      </c>
-      <c r="B18" s="6" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="C18" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="D18" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E18" s="6" t="inlineStr">
-        <is>
-          <t>12 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="12" t="inlineStr">
-        <is>
-          <t>Plan anterior (sin modalidad)</t>
-        </is>
-      </c>
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="C19" s="12" t="n">
-        <v>3</v>
-      </c>
-      <c r="D19" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E19" s="12" t="inlineStr">
-        <is>
-          <t>0 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="6" t="inlineStr">
-        <is>
-          <t>Plan anterior (sin modalidad)</t>
-        </is>
-      </c>
-      <c r="B20" s="6" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="C20" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D20" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" s="6" t="inlineStr">
-        <is>
-          <t>0 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="12" t="inlineStr">
-        <is>
-          <t>Plan anterior (sin modalidad)</t>
-        </is>
-      </c>
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="C21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="12" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="12" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
     </row>
@@ -2991,19 +3868,19 @@
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A10:E10"/>
+    <mergeCell ref="A9:E9"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C9"/>
+  <dimension ref="A1:B4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -3013,17 +3890,17 @@
     <row r="1" ht="24" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Qué se rescató de la base y qué no</t>
+          <t>Privacidad</t>
         </is>
       </c>
     </row>
     <row r="3" ht="30" customHeight="1">
-      <c r="A3" s="11" t="inlineStr">
+      <c r="A3" s="10" t="inlineStr">
         <is>
           <t>Tema</t>
         </is>
       </c>
-      <c r="B3" s="11" t="inlineStr">
+      <c r="B3" s="10" t="inlineStr">
         <is>
           <t>Detalle</t>
         </is>
@@ -3032,78 +3909,18 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Fuente</t>
+          <t>Privacidad</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>HojaVidaEgresados.xlsx (OATI): 7 hojas — datos básicos, experiencia docente, experiencia profesional, grupos de investigación, productos de investigación, publicación de obras y segunda lengua. Registros: {'datos basicos': 146, 'experiencia docente': 1019, 'experiencia profesional': 574, 'grupos investigacion': 213, 'productos investigacion': 237, 'publicacion de obras': 2, 'segunda lengua': 93}.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="12" t="inlineStr">
-        <is>
-          <t>Qué sí aporta</t>
-        </is>
-      </c>
-      <c r="B5" s="12" t="inlineStr">
-        <is>
-          <t>Trayectoria profesional y docente, vinculación laboral marcada como actual, participación en grupos/proyectos, ponencias y patentes, y nivel de segunda lengua. Permite caracterizar el impacto profesional, académico y científico.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="6" t="inlineStr">
-        <is>
-          <t>Qué no aporta</t>
-        </is>
-      </c>
-      <c r="B6" s="6" t="inlineStr">
-        <is>
-          <t>El sector en el que laboran hoy los egresados 2022-2026 (el formulario pedido a la OATI sigue pendiente), fechas de actualización de la hoja de vida y datos de contacto vigentes.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="12" t="inlineStr">
-        <is>
-          <t>Separación por modalidad</t>
-        </is>
-      </c>
-      <c r="B7" s="12" t="inlineStr">
-        <is>
-          <t>Cruce por documento con Cóndor y las bases MCIC. Los egresados del plan anterior y los que no aparecen en Cóndor no tienen modalidad.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="6" t="inlineStr">
-        <is>
-          <t>Privacidad</t>
-        </is>
-      </c>
-      <c r="B8" s="6" t="inlineStr">
-        <is>
           <t>Este informe no incluye nombres, documentos, fechas de nacimiento, correos ni teléfonos; las instituciones se agregan sin asociarlas a personas.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="12" t="inlineStr">
-        <is>
-          <t>Calidad de los datos</t>
-        </is>
-      </c>
-      <c r="B9" s="12" t="inlineStr">
-        <is>
-          <t>El tipo de entidad (pública/privada/mixta) viene del registro del propio egresado y tiene inconsistencias; el sector es una estimación por palabras clave.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A1:C1"/>
+    <mergeCell ref="A1:B1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/Data/Bronze/MCIC-PROFUNDIZACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 4. EGRESADOS/e. Caracterización e impacto de los egresados/F4_Egresados_Impacto_Profundizacion.xlsx
+++ b/Data/Bronze/MCIC-PROFUNDIZACION/Procesos de Renocavion y acreditación/Plan de Mejoramiento/FACTOR 4. EGRESADOS/e. Caracterización e impacto de los egresados/F4_Egresados_Impacto_Profundizacion.xlsx
@@ -715,7 +715,7 @@
         </is>
       </c>
       <c r="C13" s="9" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="E13" s="9" t="inlineStr">
         <is>
@@ -1273,7 +1273,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H117"/>
+  <dimension ref="A1:H122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="64" customWidth="1" min="1" max="1"/>
@@ -1296,7 +1296,7 @@
     <row r="2" ht="16" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>7 respuestas de egresados de Profundización. Sin nombres, documentos ni organizaciones; el texto libre no se publica.</t>
+          <t>9 respuestas de egresados de Profundización. Sin nombres, documentos ni organizaciones; el texto libre no se publica.</t>
         </is>
       </c>
     </row>
@@ -1335,7 +1335,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>14 %</t>
+          <t>11 %</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1350,7 @@
       </c>
       <c r="C7" s="11" t="inlineStr">
         <is>
-          <t>14 %</t>
+          <t>11 %</t>
         </is>
       </c>
     </row>
@@ -1361,11 +1361,11 @@
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>29 %</t>
+          <t>33 %</t>
         </is>
       </c>
     </row>
@@ -1376,11 +1376,11 @@
         </is>
       </c>
       <c r="B9" s="11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C9" s="11" t="inlineStr">
         <is>
-          <t>43 %</t>
+          <t>44 %</t>
         </is>
       </c>
     </row>
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>57 %</t>
+          <t>44 %</t>
         </is>
       </c>
     </row>
@@ -1430,11 +1430,11 @@
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>29 %</t>
+          <t>33 %</t>
         </is>
       </c>
     </row>
@@ -1445,11 +1445,11 @@
         </is>
       </c>
       <c r="B15" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C15" s="6" t="inlineStr">
         <is>
-          <t>14 %</t>
+          <t>22 %</t>
         </is>
       </c>
     </row>
@@ -1488,7 +1488,7 @@
       </c>
       <c r="C19" s="6" t="inlineStr">
         <is>
-          <t>29 %</t>
+          <t>22 %</t>
         </is>
       </c>
     </row>
@@ -1503,7 +1503,7 @@
       </c>
       <c r="C20" s="11" t="inlineStr">
         <is>
-          <t>29 %</t>
+          <t>22 %</t>
         </is>
       </c>
     </row>
@@ -1518,7 +1518,7 @@
       </c>
       <c r="C21" s="6" t="inlineStr">
         <is>
-          <t>14 %</t>
+          <t>11 %</t>
         </is>
       </c>
     </row>
@@ -1533,7 +1533,7 @@
       </c>
       <c r="C22" s="11" t="inlineStr">
         <is>
-          <t>14 %</t>
+          <t>11 %</t>
         </is>
       </c>
     </row>
@@ -1548,175 +1548,175 @@
       </c>
       <c r="C23" s="6" t="inlineStr">
         <is>
-          <t>14 %</t>
+          <t>11 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="11" t="inlineStr">
+        <is>
+          <t>GICOGE</t>
+        </is>
+      </c>
+      <c r="B24" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C24" s="11" t="inlineStr">
+        <is>
+          <t>11 %</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="3" t="inlineStr">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>DIMSI</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>11 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
         <is>
           <t>Situación principal actual</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="10" t="inlineStr">
+    <row r="28" ht="30" customHeight="1">
+      <c r="A28" s="10" t="inlineStr">
         <is>
           <t>Respuesta</t>
         </is>
       </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>Egresados</t>
         </is>
       </c>
-      <c r="C26" s="10" t="inlineStr">
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="6" t="inlineStr">
-        <is>
-          <t>Docente</t>
-        </is>
-      </c>
-      <c r="B27" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C27" s="6" t="inlineStr">
-        <is>
-          <t>29 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="11" t="inlineStr">
-        <is>
-          <t>Empleado(a)</t>
-        </is>
-      </c>
-      <c r="B28" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
-        <is>
-          <t>29 %</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
         <is>
-          <t>Independiente/consultor(a)</t>
+          <t>Empleado(a)</t>
         </is>
       </c>
       <c r="B29" s="6" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C29" s="6" t="inlineStr">
         <is>
-          <t>29 %</t>
+          <t>44 %</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="11" t="inlineStr">
         <is>
+          <t>Docente</t>
+        </is>
+      </c>
+      <c r="B30" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C30" s="11" t="inlineStr">
+        <is>
+          <t>22 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Independiente/consultor(a)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>22 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="11" t="inlineStr">
+        <is>
           <t>Empleado y Docente</t>
         </is>
       </c>
-      <c r="B30" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
-        <is>
-          <t>14 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
+      <c r="B32" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>11 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
         <is>
           <t>Sector en el que se desempeña</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="10" t="inlineStr">
+    <row r="35" ht="30" customHeight="1">
+      <c r="A35" s="10" t="inlineStr">
         <is>
           <t>Respuesta</t>
         </is>
       </c>
-      <c r="B33" s="10" t="inlineStr">
+      <c r="B35" s="10" t="inlineStr">
         <is>
           <t>Egresados</t>
         </is>
       </c>
-      <c r="C33" s="10" t="inlineStr">
+      <c r="C35" s="10" t="inlineStr">
         <is>
           <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="6" t="inlineStr">
-        <is>
-          <t>Educación Superior</t>
-        </is>
-      </c>
-      <c r="B34" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6" t="inlineStr">
-        <is>
-          <t>29 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
-        <is>
-          <t>Servicios Financieros</t>
-        </is>
-      </c>
-      <c r="B35" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C35" s="11" t="inlineStr">
-        <is>
-          <t>14 %</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
         <is>
-          <t>TIC</t>
+          <t>Educación Superior</t>
         </is>
       </c>
       <c r="B36" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C36" s="6" t="inlineStr">
         <is>
-          <t>14 %</t>
+          <t>22 %</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="11" t="inlineStr">
         <is>
-          <t>Investigación y desarrollo</t>
+          <t>TIC</t>
         </is>
       </c>
       <c r="B37" s="11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C37" s="11" t="inlineStr">
         <is>
-          <t>14 %</t>
+          <t>22 %</t>
         </is>
       </c>
     </row>
@@ -1727,80 +1727,80 @@
         </is>
       </c>
       <c r="B38" s="6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="C38" s="6" t="inlineStr">
         <is>
-          <t>14 %</t>
+          <t>22 %</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="11" t="inlineStr">
         <is>
+          <t>Servicios Financieros</t>
+        </is>
+      </c>
+      <c r="B39" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C39" s="11" t="inlineStr">
+        <is>
+          <t>11 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Investigación y desarrollo</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C40" s="6" t="inlineStr">
+        <is>
+          <t>11 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="11" t="inlineStr">
+        <is>
           <t>Industria</t>
         </is>
       </c>
-      <c r="B39" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C39" s="11" t="inlineStr">
-        <is>
-          <t>14 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
+      <c r="B41" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C41" s="11" t="inlineStr">
+        <is>
+          <t>11 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="3" t="inlineStr">
         <is>
           <t>Nivel de responsabilidad del cargo</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="10" t="inlineStr">
+    <row r="44" ht="30" customHeight="1">
+      <c r="A44" s="10" t="inlineStr">
         <is>
           <t>Respuesta</t>
         </is>
       </c>
-      <c r="B42" s="10" t="inlineStr">
+      <c r="B44" s="10" t="inlineStr">
         <is>
           <t>Egresados</t>
         </is>
       </c>
-      <c r="C42" s="10" t="inlineStr">
+      <c r="C44" s="10" t="inlineStr">
         <is>
           <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="6" t="inlineStr">
-        <is>
-          <t>Docencia</t>
-        </is>
-      </c>
-      <c r="B43" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C43" s="6" t="inlineStr">
-        <is>
-          <t>29 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="11" t="inlineStr">
-        <is>
-          <t>Dirección/jefatura</t>
-        </is>
-      </c>
-      <c r="B44" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C44" s="11" t="inlineStr">
-        <is>
-          <t>29 %</t>
         </is>
       </c>
     </row>
@@ -1811,716 +1811,737 @@
         </is>
       </c>
       <c r="B45" s="6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C45" s="6" t="inlineStr">
         <is>
-          <t>29 %</t>
+          <t>33 %</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="11" t="inlineStr">
         <is>
+          <t>Docencia</t>
+        </is>
+      </c>
+      <c r="B46" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C46" s="11" t="inlineStr">
+        <is>
+          <t>22 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Dirección/jefatura</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="C47" s="6" t="inlineStr">
+        <is>
+          <t>22 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="11" t="inlineStr">
+        <is>
           <t>Emprendimiento</t>
         </is>
       </c>
-      <c r="B46" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C46" s="11" t="inlineStr">
-        <is>
-          <t>14 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="3" t="inlineStr">
+      <c r="B48" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C48" s="11" t="inlineStr">
+        <is>
+          <t>11 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Coordinación</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C49" s="6" t="inlineStr">
+        <is>
+          <t>11 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
         <is>
           <t>Relación de la actividad actual con la formación recibida</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="10" t="inlineStr">
+    <row r="52" ht="30" customHeight="1">
+      <c r="A52" s="10" t="inlineStr">
         <is>
           <t>Respuesta</t>
         </is>
       </c>
-      <c r="B49" s="10" t="inlineStr">
+      <c r="B52" s="10" t="inlineStr">
         <is>
           <t>Egresados</t>
         </is>
       </c>
-      <c r="C49" s="10" t="inlineStr">
+      <c r="C52" s="10" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="6" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
         <is>
           <t>Muy Relacionada</t>
         </is>
       </c>
-      <c r="B50" s="6" t="n">
+      <c r="B53" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="C53" s="6" t="inlineStr">
+        <is>
+          <t>67 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>Totalmente Relacionada</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>22 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>No relacionada</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>11 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="3" t="inlineStr">
+        <is>
+          <t>Aporte de la MCIC a su desarrollo (número de egresados por nivel)</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="30" customHeight="1">
+      <c r="A58" s="10" t="inlineStr">
+        <is>
+          <t>Dimensión</t>
+        </is>
+      </c>
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>Muy alto</t>
+        </is>
+      </c>
+      <c r="C58" s="10" t="inlineStr">
+        <is>
+          <t>Alto</t>
+        </is>
+      </c>
+      <c r="D58" s="10" t="inlineStr">
+        <is>
+          <t>Medio</t>
+        </is>
+      </c>
+      <c r="E58" s="10" t="inlineStr">
+        <is>
+          <t>Bajo</t>
+        </is>
+      </c>
+      <c r="F58" s="10" t="inlineStr">
+        <is>
+          <t>Ningún aporte</t>
+        </is>
+      </c>
+      <c r="G58" s="10" t="inlineStr">
+        <is>
+          <t>% Alto o Muy alto</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="6" t="inlineStr">
+        <is>
+          <t>Desarrollo profesional</t>
+        </is>
+      </c>
+      <c r="B59" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C50" s="6" t="inlineStr">
-        <is>
-          <t>57 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="11" t="inlineStr">
-        <is>
-          <t>Totalmente Relacionada</t>
-        </is>
-      </c>
-      <c r="B51" s="11" t="n">
+      <c r="C59" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G59" s="6" t="inlineStr">
+        <is>
+          <t>100 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>Acceso a nuevas oportunidades laborales</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C60" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D60" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E60" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F60" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G60" s="11" t="inlineStr">
+        <is>
+          <t>67 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Capacidad para resolver problemas complejos</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="C61" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C51" s="11" t="inlineStr">
-        <is>
-          <t>29 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="6" t="inlineStr">
-        <is>
-          <t>No relacionada</t>
-        </is>
-      </c>
-      <c r="B52" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C52" s="6" t="inlineStr">
-        <is>
-          <t>14 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>Aporte de la MCIC a su desarrollo (número de egresados por nivel)</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="10" t="inlineStr">
-        <is>
-          <t>Dimensión</t>
-        </is>
-      </c>
-      <c r="B55" s="10" t="inlineStr">
-        <is>
-          <t>Muy alto</t>
-        </is>
-      </c>
-      <c r="C55" s="10" t="inlineStr">
-        <is>
-          <t>Alto</t>
-        </is>
-      </c>
-      <c r="D55" s="10" t="inlineStr">
-        <is>
-          <t>Medio</t>
-        </is>
-      </c>
-      <c r="E55" s="10" t="inlineStr">
-        <is>
-          <t>Bajo</t>
-        </is>
-      </c>
-      <c r="F55" s="10" t="inlineStr">
-        <is>
-          <t>Ningún aporte</t>
-        </is>
-      </c>
-      <c r="G55" s="10" t="inlineStr">
-        <is>
-          <t>% Alto o Muy alto</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="6" t="inlineStr">
-        <is>
-          <t>Desarrollo profesional</t>
-        </is>
-      </c>
-      <c r="B56" s="6" t="n">
+      <c r="D61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E61" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F61" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="6" t="inlineStr">
+        <is>
+          <t>78 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>Desarrollo de capacidades de investigación</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C62" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D62" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G62" s="11" t="inlineStr">
+        <is>
+          <t>89 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Innovación y desarrollo tecnológico</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="C56" s="6" t="n">
+      <c r="C63" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D63" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="6" t="inlineStr">
+        <is>
+          <t>89 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="11" t="inlineStr">
+        <is>
+          <t>Liderazgo de proyectos</t>
+        </is>
+      </c>
+      <c r="B64" s="11" t="n">
         <v>3</v>
       </c>
-      <c r="D56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="6" t="inlineStr">
-        <is>
-          <t>100 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>Acceso a nuevas oportunidades laborales</t>
-        </is>
-      </c>
-      <c r="B57" s="11" t="n">
+      <c r="C64" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D64" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="E64" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="F64" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t>56 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Toma de decisiones basada en información</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C57" s="11" t="n">
+      <c r="C65" s="6" t="n">
+        <v>5</v>
+      </c>
+      <c r="D65" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="6" t="inlineStr">
+        <is>
+          <t>89 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="11" t="inlineStr">
+        <is>
+          <t>Trabajo interdisciplinario</t>
+        </is>
+      </c>
+      <c r="B66" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C66" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="D66" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D57" s="11" t="n">
+      <c r="E66" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F66" s="11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="11" t="inlineStr">
+        <is>
+          <t>67 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="6" t="inlineStr">
+        <is>
+          <t>Desarrollo de redes académicas/profesionales</t>
+        </is>
+      </c>
+      <c r="B67" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C67" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D67" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="E67" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G67" s="6" t="inlineStr">
+        <is>
+          <t>44 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="11" t="inlineStr">
+        <is>
+          <t>Continuación de estudios de formación avanzada</t>
+        </is>
+      </c>
+      <c r="B68" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="E57" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G57" s="11" t="inlineStr">
-        <is>
-          <t>71 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="6" t="inlineStr">
-        <is>
-          <t>Capacidad para resolver problemas complejos</t>
-        </is>
-      </c>
-      <c r="B58" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E58" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F58" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G58" s="6" t="inlineStr">
-        <is>
-          <t>71 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="11" t="inlineStr">
-        <is>
-          <t>Desarrollo de capacidades de investigación</t>
-        </is>
-      </c>
-      <c r="B59" s="11" t="n">
+      <c r="C68" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="D68" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="E68" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="F68" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="G68" s="11" t="inlineStr">
+        <is>
+          <t>44 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Generación o transferencia de conocimiento</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C69" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="D69" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="E69" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="G69" s="6" t="inlineStr">
+        <is>
+          <t>78 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="3" t="inlineStr">
+        <is>
+          <t>Actividades después de graduarse (selección múltiple)</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="30" customHeight="1">
+      <c r="A72" s="10" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="B72" s="10" t="inlineStr">
+        <is>
+          <t>Egresados</t>
+        </is>
+      </c>
+      <c r="C72" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Desarrollo de software o soluciones tecnológicas</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="C59" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G59" s="11" t="inlineStr">
-        <is>
-          <t>86 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="6" t="inlineStr">
-        <is>
-          <t>Innovación y desarrollo tecnológico</t>
-        </is>
-      </c>
-      <c r="B60" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="C60" s="6" t="n">
+      <c r="C73" s="6" t="inlineStr">
+        <is>
+          <t>67 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="11" t="inlineStr">
+        <is>
+          <t>Docencia universitaria</t>
+        </is>
+      </c>
+      <c r="B74" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C74" s="11" t="inlineStr">
+        <is>
+          <t>33 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Innovaciones o mejoras de procesos</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C75" s="6" t="inlineStr">
+        <is>
+          <t>33 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="11" t="inlineStr">
+        <is>
+          <t>Participación en proyectos con entidades públicas o privadas</t>
+        </is>
+      </c>
+      <c r="B76" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D60" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="6" t="inlineStr">
-        <is>
-          <t>86 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="11" t="inlineStr">
-        <is>
-          <t>Liderazgo de proyectos</t>
-        </is>
-      </c>
-      <c r="B61" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C61" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D61" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E61" s="11" t="n">
+      <c r="C76" s="11" t="inlineStr">
+        <is>
+          <t>22 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Dirección o participación en proyectos de impacto social</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="F61" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="11" t="inlineStr">
-        <is>
-          <t>57 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="6" t="inlineStr">
-        <is>
-          <t>Toma de decisiones basada en información</t>
-        </is>
-      </c>
-      <c r="B62" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C62" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="D62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="E62" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="F62" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="6" t="inlineStr">
-        <is>
-          <t>86 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="11" t="inlineStr">
-        <is>
-          <t>Trabajo interdisciplinario</t>
-        </is>
-      </c>
-      <c r="B63" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C63" s="11" t="n">
+      <c r="C77" s="6" t="inlineStr">
+        <is>
+          <t>22 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="11" t="inlineStr">
+        <is>
+          <t>Participación en redes académicas o profesionales</t>
+        </is>
+      </c>
+      <c r="B78" s="11" t="n">
         <v>2</v>
       </c>
-      <c r="D63" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="E63" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F63" s="11" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="11" t="inlineStr">
-        <is>
-          <t>71 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="6" t="inlineStr">
-        <is>
-          <t>Desarrollo de redes académicas/profesionales</t>
-        </is>
-      </c>
-      <c r="B64" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="E64" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G64" s="6" t="inlineStr">
-        <is>
-          <t>43 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="11" t="inlineStr">
-        <is>
-          <t>Continuación de estudios de formación avanzada</t>
-        </is>
-      </c>
-      <c r="B65" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C65" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="D65" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="E65" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="F65" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="G65" s="11" t="inlineStr">
-        <is>
-          <t>43 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="6" t="inlineStr">
-        <is>
-          <t>Generación o transferencia de conocimiento</t>
-        </is>
-      </c>
-      <c r="B66" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C66" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="D66" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="E66" s="6" t="n">
-        <v>0</v>
-      </c>
-      <c r="F66" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="G66" s="6" t="inlineStr">
-        <is>
-          <t>71 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="3" t="inlineStr">
-        <is>
-          <t>Actividades después de graduarse (selección múltiple)</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="10" t="inlineStr">
-        <is>
-          <t>Respuesta</t>
-        </is>
-      </c>
-      <c r="B69" s="10" t="inlineStr">
-        <is>
-          <t>Egresados</t>
-        </is>
-      </c>
-      <c r="C69" s="10" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="6" t="inlineStr">
-        <is>
-          <t>Desarrollo de software o soluciones tecnológicas</t>
-        </is>
-      </c>
-      <c r="B70" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C70" s="6" t="inlineStr">
-        <is>
-          <t>71 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="11" t="inlineStr">
-        <is>
-          <t>Docencia universitaria</t>
-        </is>
-      </c>
-      <c r="B71" s="11" t="n">
-        <v>3</v>
-      </c>
-      <c r="C71" s="11" t="inlineStr">
-        <is>
-          <t>43 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="6" t="inlineStr">
-        <is>
-          <t>Innovaciones o mejoras de procesos</t>
-        </is>
-      </c>
-      <c r="B72" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C72" s="6" t="inlineStr">
-        <is>
-          <t>29 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" s="11" t="inlineStr">
-        <is>
-          <t>Participación en proyectos con entidades públicas o privadas</t>
-        </is>
-      </c>
-      <c r="B73" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C73" s="11" t="inlineStr">
-        <is>
-          <t>29 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" s="6" t="inlineStr">
-        <is>
-          <t>Dirección o participación en proyectos de impacto social</t>
-        </is>
-      </c>
-      <c r="B74" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C74" s="6" t="inlineStr">
-        <is>
-          <t>29 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" s="11" t="inlineStr">
-        <is>
-          <t>Participación en redes académicas o profesionales</t>
-        </is>
-      </c>
-      <c r="B75" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C75" s="11" t="inlineStr">
-        <is>
-          <t>29 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" s="6" t="inlineStr">
+      <c r="C78" s="11" t="inlineStr">
+        <is>
+          <t>22 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
         <is>
           <t>Patentes, registros de software u otros productos de propiedad intelectual</t>
         </is>
       </c>
-      <c r="B76" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C76" s="6" t="inlineStr">
-        <is>
-          <t>14 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="11" t="inlineStr">
+      <c r="B79" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C79" s="6" t="inlineStr">
+        <is>
+          <t>11 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="11" t="inlineStr">
         <is>
           <t>Consultorías especializadas</t>
         </is>
       </c>
-      <c r="B77" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C77" s="11" t="inlineStr">
-        <is>
-          <t>14 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="6" t="inlineStr">
+      <c r="B80" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C80" s="11" t="inlineStr">
+        <is>
+          <t>11 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
         <is>
           <t>Dirección de trabajos de grado</t>
         </is>
       </c>
-      <c r="B78" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C78" s="6" t="inlineStr">
-        <is>
-          <t>14 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="11" t="inlineStr">
+      <c r="B81" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C81" s="6" t="inlineStr">
+        <is>
+          <t>11 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="11" t="inlineStr">
         <is>
           <t>Ponencias en eventos internacionales.</t>
         </is>
       </c>
-      <c r="B79" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C79" s="11" t="inlineStr">
-        <is>
-          <t>14 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="6" t="inlineStr">
+      <c r="B82" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C82" s="11" t="inlineStr">
+        <is>
+          <t>11 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="6" t="inlineStr">
         <is>
           <t>Creación de empresa/emprendimiento</t>
         </is>
       </c>
-      <c r="B80" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C80" s="6" t="inlineStr">
-        <is>
-          <t>14 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="11" t="inlineStr">
+      <c r="B83" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C83" s="6" t="inlineStr">
+        <is>
+          <t>11 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="11" t="inlineStr">
         <is>
           <t>Ponencias en eventos nacionales.</t>
         </is>
       </c>
-      <c r="B81" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C81" s="11" t="inlineStr">
-        <is>
-          <t>14 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" s="6" t="inlineStr">
+      <c r="B84" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C84" s="11" t="inlineStr">
+        <is>
+          <t>11 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="6" t="inlineStr">
         <is>
           <t>Jurado de Tesis</t>
         </is>
       </c>
-      <c r="B82" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="C82" s="6" t="inlineStr">
-        <is>
-          <t>14 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="3" t="inlineStr">
-        <is>
-          <t>Formación continuada después de graduarse (selección múltiple)</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="30" customHeight="1">
-      <c r="A85" s="10" t="inlineStr">
-        <is>
-          <t>Respuesta</t>
-        </is>
-      </c>
-      <c r="B85" s="10" t="inlineStr">
-        <is>
-          <t>Egresados</t>
-        </is>
-      </c>
-      <c r="C85" s="10" t="inlineStr">
-        <is>
-          <t>%</t>
+      <c r="B85" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C85" s="6" t="inlineStr">
+        <is>
+          <t>11 %</t>
         </is>
       </c>
     </row>
     <row r="86">
-      <c r="A86" s="6" t="inlineStr">
-        <is>
-          <t>No</t>
-        </is>
-      </c>
-      <c r="B86" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="C86" s="6" t="inlineStr">
-        <is>
-          <t>100 %</t>
+      <c r="A86" s="11" t="inlineStr">
+        <is>
+          <t>Participación en proyectos de investigación</t>
+        </is>
+      </c>
+      <c r="B86" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C86" s="11" t="inlineStr">
+        <is>
+          <t>11 %</t>
         </is>
       </c>
     </row>
     <row r="87">
-      <c r="A87" s="11" t="inlineStr">
-        <is>
-          <t>Curso / diplomados</t>
-        </is>
-      </c>
-      <c r="B87" s="11" t="n">
-        <v>1</v>
-      </c>
-      <c r="C87" s="11" t="inlineStr">
-        <is>
-          <t>14 %</t>
+      <c r="A87" s="6" t="inlineStr">
+        <is>
+          <t>Publicaciones científicas o académicas</t>
+        </is>
+      </c>
+      <c r="B87" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C87" s="6" t="inlineStr">
+        <is>
+          <t>11 %</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="3" t="inlineStr">
         <is>
-          <t>Pertenece o ha pertenecido a un grupo de investigación</t>
+          <t>Formación continuada después de graduarse (selección múltiple)</t>
         </is>
       </c>
     </row>
@@ -2548,18 +2569,18 @@
         </is>
       </c>
       <c r="B91" s="6" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="C91" s="6" t="inlineStr">
         <is>
-          <t>86 %</t>
+          <t>100 %</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="11" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Curso / diplomados</t>
         </is>
       </c>
       <c r="B92" s="11" t="n">
@@ -2567,14 +2588,14 @@
       </c>
       <c r="C92" s="11" t="inlineStr">
         <is>
-          <t>14 %</t>
+          <t>11 %</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="3" t="inlineStr">
         <is>
-          <t>Ha publicado productos académicos o científicos después de graduarse</t>
+          <t>Pertenece o ha pertenecido a un grupo de investigación</t>
         </is>
       </c>
     </row>
@@ -2606,183 +2627,183 @@
       </c>
       <c r="C96" s="6" t="inlineStr">
         <is>
+          <t>78 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="11" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="B97" s="11" t="n">
+        <v>2</v>
+      </c>
+      <c r="C97" s="11" t="inlineStr">
+        <is>
+          <t>22 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="3" t="inlineStr">
+        <is>
+          <t>Ha publicado productos académicos o científicos después de graduarse</t>
+        </is>
+      </c>
+    </row>
+    <row r="100" ht="30" customHeight="1">
+      <c r="A100" s="10" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="B100" s="10" t="inlineStr">
+        <is>
+          <t>Egresados</t>
+        </is>
+      </c>
+      <c r="C100" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="6" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+      <c r="B101" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="C101" s="6" t="inlineStr">
+        <is>
           <t>100 %</t>
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="3" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="3" t="inlineStr">
         <is>
           <t>Valoración de la formación (escala 1 a 5)</t>
         </is>
       </c>
     </row>
-    <row r="99" ht="30" customHeight="1">
-      <c r="A99" s="10" t="inlineStr">
+    <row r="104" ht="30" customHeight="1">
+      <c r="A104" s="10" t="inlineStr">
         <is>
           <t>Aspecto</t>
         </is>
       </c>
-      <c r="B99" s="10" t="inlineStr">
+      <c r="B104" s="10" t="inlineStr">
         <is>
           <t>Promedio</t>
         </is>
       </c>
-      <c r="C99" s="10" t="inlineStr">
+      <c r="C104" s="10" t="inlineStr">
         <is>
           <t>Respuestas</t>
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="6" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="6" t="inlineStr">
         <is>
           <t>Pertinencia de la formación recibida</t>
         </is>
       </c>
-      <c r="B100" s="6" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="C100" s="6" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" s="11" t="inlineStr">
+      <c r="B105" s="6" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="C105" s="6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="11" t="inlineStr">
         <is>
           <t>Actualidad de los conocimientos adquiridos</t>
         </is>
       </c>
-      <c r="B101" s="11" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="C101" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" s="6" t="inlineStr">
+      <c r="B106" s="11" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="C106" s="11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="6" t="inlineStr">
         <is>
           <t>Contribución de la Maestría a su desempeño profesional</t>
         </is>
       </c>
-      <c r="B102" s="6" t="n">
-        <v>4.71</v>
-      </c>
-      <c r="C102" s="6" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" s="11" t="inlineStr">
+      <c r="B107" s="6" t="n">
+        <v>4.67</v>
+      </c>
+      <c r="C107" s="6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="11" t="inlineStr">
         <is>
           <t>Contribución a sus capacidades investigativas</t>
         </is>
       </c>
-      <c r="B103" s="11" t="n">
-        <v>4.43</v>
-      </c>
-      <c r="C103" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" s="6" t="inlineStr">
+      <c r="B108" s="11" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="C108" s="11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="6" t="inlineStr">
         <is>
           <t>Contribución a su capacidad de innovación</t>
         </is>
       </c>
-      <c r="B104" s="6" t="n">
-        <v>4.29</v>
-      </c>
-      <c r="C104" s="6" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" s="11" t="inlineStr">
+      <c r="B109" s="6" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="C109" s="6" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" s="11" t="inlineStr">
         <is>
           <t>Reconocimiento de la MCIC en su entorno profesional</t>
         </is>
       </c>
-      <c r="B105" s="11" t="n">
+      <c r="B110" s="11" t="n">
         <v>4</v>
       </c>
-      <c r="C105" s="11" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" s="6" t="inlineStr">
+      <c r="C110" s="11" t="n">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" s="6" t="inlineStr">
         <is>
           <t>Correspondencia entre la formación recibida y las necesidades actuales del entorno</t>
         </is>
       </c>
-      <c r="B106" s="6" t="n">
-        <v>4.57</v>
-      </c>
-      <c r="C106" s="6" t="n">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" s="3" t="inlineStr">
-        <is>
-          <t>¿Recomendaría la MCIC a otros profesionales?</t>
-        </is>
-      </c>
-    </row>
-    <row r="109" ht="30" customHeight="1">
-      <c r="A109" s="10" t="inlineStr">
-        <is>
-          <t>Respuesta</t>
-        </is>
-      </c>
-      <c r="B109" s="10" t="inlineStr">
-        <is>
-          <t>Egresados</t>
-        </is>
-      </c>
-      <c r="C109" s="10" t="inlineStr">
-        <is>
-          <t>%</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" s="6" t="inlineStr">
-        <is>
-          <t>Definitivamente sí</t>
-        </is>
-      </c>
-      <c r="B110" s="6" t="n">
-        <v>5</v>
-      </c>
-      <c r="C110" s="6" t="inlineStr">
-        <is>
-          <t>71 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" s="11" t="inlineStr">
-        <is>
-          <t>Probablemente sí</t>
-        </is>
-      </c>
-      <c r="B111" s="11" t="n">
-        <v>2</v>
-      </c>
-      <c r="C111" s="11" t="inlineStr">
-        <is>
-          <t>29 %</t>
-        </is>
+      <c r="B111" s="6" t="n">
+        <v>4.44</v>
+      </c>
+      <c r="C111" s="6" t="n">
+        <v>9</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="3" t="inlineStr">
         <is>
-          <t>¿Ha generado algún impacto en su entorno a partir de su formación?</t>
+          <t>¿Recomendaría la MCIC a otros profesionales?</t>
         </is>
       </c>
     </row>
@@ -2806,45 +2827,99 @@
     <row r="115">
       <c r="A115" s="6" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>Definitivamente sí</t>
         </is>
       </c>
       <c r="B115" s="6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="C115" s="6" t="inlineStr">
         <is>
-          <t>43 %</t>
+          <t>56 %</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="11" t="inlineStr">
         <is>
+          <t>Probablemente sí</t>
+        </is>
+      </c>
+      <c r="B116" s="11" t="n">
+        <v>4</v>
+      </c>
+      <c r="C116" s="11" t="inlineStr">
+        <is>
+          <t>44 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="3" t="inlineStr">
+        <is>
+          <t>¿Ha generado algún impacto en su entorno a partir de su formación?</t>
+        </is>
+      </c>
+    </row>
+    <row r="119" ht="30" customHeight="1">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>Respuesta</t>
+        </is>
+      </c>
+      <c r="B119" s="10" t="inlineStr">
+        <is>
+          <t>Egresados</t>
+        </is>
+      </c>
+      <c r="C119" s="10" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="6" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="B120" s="6" t="n">
+        <v>4</v>
+      </c>
+      <c r="C120" s="6" t="inlineStr">
+        <is>
+          <t>44 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="11" t="inlineStr">
+        <is>
+          <t>Parcialmente</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C121" s="11" t="inlineStr">
+        <is>
+          <t>33 %</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="6" t="inlineStr">
+        <is>
           <t>No</t>
         </is>
       </c>
-      <c r="B116" s="11" t="n">
+      <c r="B122" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="C116" s="11" t="inlineStr">
-        <is>
-          <t>29 %</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" s="6" t="inlineStr">
-        <is>
-          <t>Parcialmente</t>
-        </is>
-      </c>
-      <c r="B117" s="6" t="n">
-        <v>2</v>
-      </c>
-      <c r="C117" s="6" t="inlineStr">
-        <is>
-          <t>29 %</t>
+      <c r="C122" s="6" t="inlineStr">
+        <is>
+          <t>22 %</t>
         </is>
       </c>
     </row>
@@ -2852,19 +2927,19 @@
   <mergeCells count="17">
     <mergeCell ref="A94:H94"/>
     <mergeCell ref="A4:H4"/>
-    <mergeCell ref="A48:H48"/>
-    <mergeCell ref="A84:H84"/>
-    <mergeCell ref="A25:H25"/>
+    <mergeCell ref="A34:H34"/>
+    <mergeCell ref="A43:H43"/>
+    <mergeCell ref="A57:H57"/>
+    <mergeCell ref="A2:H2"/>
+    <mergeCell ref="A51:H51"/>
+    <mergeCell ref="A71:H71"/>
+    <mergeCell ref="A99:H99"/>
+    <mergeCell ref="A103:H103"/>
     <mergeCell ref="A113:H113"/>
-    <mergeCell ref="A2:H2"/>
-    <mergeCell ref="A54:H54"/>
-    <mergeCell ref="A98:H98"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A68:H68"/>
     <mergeCell ref="A11:H11"/>
-    <mergeCell ref="A108:H108"/>
+    <mergeCell ref="A118:H118"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A32:H32"/>
+    <mergeCell ref="A27:H27"/>
     <mergeCell ref="A89:H89"/>
     <mergeCell ref="A17:H17"/>
   </mergeCells>
